--- a/data/media_articles.xlsx
+++ b/data/media_articles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sepehrakbari/Desktop/temp-jrp/data/colleges_final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sepehrakbari/Projects/enrollment-cliff/src/topic_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2593B00-BA30-1541-8A10-D7FB5E84CDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEDE0B3-BDA6-C74B-8F86-848629B67D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="168">
   <si>
     <t>index</t>
   </si>
@@ -512,6 +512,18 @@
   </si>
   <si>
     <t>https://www.highereddive.com/news/cardinal-stritch-university-campus-purchased-for-24m/689752/</t>
+  </si>
+  <si>
+    <t>Hampshire College</t>
+  </si>
+  <si>
+    <t>Anna Maria College</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/hampshire-college-closure-announcement/817499/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/anna-maria-college-massachusetts-closure/818492/</t>
   </si>
 </sst>
 </file>
@@ -597,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -615,6 +627,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -919,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -2238,8 +2254,48 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D67" s="6"/>
+    <row r="67" spans="1:6" s="8" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>166018</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>164492</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D69" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
